--- a/artfynd/A 60670-2022 artfynd.xlsx
+++ b/artfynd/A 60670-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60670-2022 artfynd.xlsx
+++ b/artfynd/A 60670-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101690122</v>
+        <v>101690135</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590067.394925256</v>
+        <v>589988</v>
       </c>
       <c r="R2" t="n">
-        <v>6994764.420250903</v>
+        <v>6994968</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2022-06-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101690169</v>
+        <v>101690122</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590122.3444540791</v>
+        <v>590068</v>
       </c>
       <c r="R3" t="n">
-        <v>6994846.214933682</v>
+        <v>6994764</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +851,9 @@
           <t>2022-06-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,12 +888,7 @@
         <v>101690158</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590081.534254425</v>
+        <v>590082</v>
       </c>
       <c r="R4" t="n">
-        <v>6994909.477549023</v>
+        <v>6994910</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,19 +956,9 @@
           <t>2022-06-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101690145</v>
+        <v>101690169</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590001.2029981263</v>
+        <v>590123</v>
       </c>
       <c r="R5" t="n">
-        <v>6995022.432055499</v>
+        <v>6994846</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,24 +1061,9 @@
           <t>2022-06-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på gammal björk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101690135</v>
+        <v>101690145</v>
       </c>
       <c r="B6" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589988.1781638986</v>
+        <v>590001</v>
       </c>
       <c r="R6" t="n">
-        <v>6994968.107691403</v>
+        <v>6995023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,19 +1166,14 @@
           <t>2022-06-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-08</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på gammal björk</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 60670-2022 artfynd.xlsx
+++ b/artfynd/A 60670-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101690135</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101690122</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101690158</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101690169</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101690145</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>